--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/nov-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/nov-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M259"/>
+  <dimension ref="A1:M250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2039,7 +2039,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5520-10644-CM25</t>
+          <t>2418-96-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>22514.92</v>
+        <v>3069.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1658-4808-CM25</t>
+          <t>5520-10644-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8498.98</v>
+        <v>22514.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>711841-673-CM25</t>
+          <t>3992-253-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,32 +2181,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8072.48</v>
+        <v>9356.24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3992-253-CM25</t>
+          <t>2735-1638-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9356.24</v>
+        <v>17728.62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2735-1638-CM25</t>
+          <t>3863-472-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,27 +2308,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17728.62</v>
+        <v>43359.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3863-472-CM25</t>
+          <t>1658-4911-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>43359.42</v>
+        <v>14443.21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1658-4911-CM25</t>
+          <t>1658-4808-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14443.21</v>
+        <v>8498.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2418-96-CM25</t>
+          <t>711841-673-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,27 +2491,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3069.31</v>
+        <v>8072.48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1171166-456-CM25</t>
+          <t>3604-1123-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.170.501-3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>24552.08</v>
+        <v>26655.58</v>
       </c>
     </row>
     <row r="36">
@@ -2954,7 +2954,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1171166-455-CM25</t>
+          <t>1171166-456-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3015,7 +3015,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4159-793-CM25</t>
+          <t>1171166-455-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>32327.54</v>
+        <v>24552.08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>975-469-CM25</t>
+          <t>952751-18-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>17681.71</v>
+        <v>3362.35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>952751-18-CM25</t>
+          <t>1154491-10-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.216.000-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3362.35</v>
+        <v>18829.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1154491-10-CM25</t>
+          <t>872-602-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.216.000-7</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
+          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>18829.13</v>
+        <v>2690.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>872-602-CM25</t>
+          <t>3928-1139-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Educación Municipal</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2690.83</v>
+        <v>4243.54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3928-1139-CM25</t>
+          <t>3928-1132-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4243.54</v>
+        <v>3646.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3928-1132-CM25</t>
+          <t>4159-793-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,27 +3406,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3646.06</v>
+        <v>32327.54</v>
       </c>
     </row>
     <row r="50">
@@ -3503,7 +3503,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3604-1123-CM25</t>
+          <t>975-469-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,27 +3528,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.170.501-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>26655.58</v>
+        <v>17681.71</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2328-1427-CM25</t>
+          <t>4285-262-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,27 +3589,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>23526</v>
+        <v>2882.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1019-556-CM25</t>
+          <t>1224957-1315-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>73136.89999999999</v>
+        <v>12280.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1224957-1315-CM25</t>
+          <t>2713-1116-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>12280.8</v>
+        <v>6850.66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4285-262-CM25</t>
+          <t>2328-1427-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,27 +3772,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2882.18</v>
+        <v>23526</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2713-1118-CM25</t>
+          <t>1019-556-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,27 +3833,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>19307.75</v>
+        <v>73136.89999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2713-1116-CM25</t>
+          <t>2759-1086-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3889,32 +3889,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6850.66</v>
+        <v>25320.82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2759-1086-CM25</t>
+          <t>2713-1118-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3950,32 +3950,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>25320.82</v>
+        <v>19307.75</v>
       </c>
     </row>
     <row r="59">
@@ -4113,7 +4113,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2418-94-CM25</t>
+          <t>2711-513-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4133,32 +4133,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>12730.62</v>
+        <v>33019.61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2409-1714-CM25</t>
+          <t>2418-94-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>19307.75</v>
+        <v>12730.62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3863-416-CM25</t>
+          <t>2409-1714-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4255,32 +4255,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2556.08</v>
+        <v>19307.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3863-415-CM25</t>
+          <t>3863-416-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2558.5</v>
+        <v>2556.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2711-513-CM25</t>
+          <t>3863-415-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,32 +4377,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>33019.61</v>
+        <v>2558.5</v>
       </c>
     </row>
     <row r="66">
@@ -4479,7 +4479,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4359-290-CM25</t>
+          <t>1469-3585-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,27 +4504,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8306.18</v>
+        <v>17812.87</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2859-1560-CM25</t>
+          <t>4359-290-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4560,32 +4560,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>49479.56</v>
+        <v>8306.18</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1469-3585-CM25</t>
+          <t>977-115-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4621,32 +4621,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>17812.87</v>
+        <v>3179.44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>977-115-CM25</t>
+          <t>2328-1432-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4682,32 +4682,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3179.44</v>
+        <v>5937.62</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1426037-155-CM25</t>
+          <t>2859-1560-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4748,27 +4748,27 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5114.62</v>
+        <v>49479.56</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2711-515-CM25</t>
+          <t>979-2017-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>22084.5</v>
+        <v>9162.74</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>979-2017-CM25</t>
+          <t>1426037-155-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>9162.74</v>
+        <v>5114.62</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2328-1432-CM25</t>
+          <t>1274189-504-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,32 +4926,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>70.934.900-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5937.62</v>
+        <v>17842.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1274189-504-CM25</t>
+          <t>2711-515-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4987,32 +4987,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>70.934.900-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>17842.61</v>
+        <v>22084.5</v>
       </c>
     </row>
     <row r="76">
@@ -5638,7 +5638,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5416-1342-CM25</t>
+          <t>1088-155-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5658,32 +5658,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2781.03</v>
+        <v>5383.56</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1088-155-CM25</t>
+          <t>2216-744-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5724,27 +5724,27 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5383.56</v>
+        <v>8567.879999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2216-744-CM25</t>
+          <t>2429-2875-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5785,27 +5785,27 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8567.879999999999</v>
+        <v>24981.79</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2429-2875-CM25</t>
+          <t>1592-159-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,17 +5846,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.503.000-7</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>24981.79</v>
+        <v>6900.81</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1592-159-CM25</t>
+          <t>5416-1342-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5902,32 +5902,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.503.000-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>6900.81</v>
+        <v>2781.03</v>
       </c>
     </row>
     <row r="91">
@@ -6004,7 +6004,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1057448-562-CM25</t>
+          <t>2762-1244-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,32 +6024,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>69.151.202-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>17822.87</v>
+        <v>20229.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2762-1244-CM25</t>
+          <t>3928-1244-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6085,32 +6085,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.151.202-9</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>Educación Municipal</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>20229.7</v>
+        <v>2392.22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3928-1244-CM25</t>
+          <t>1480082-10-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6146,32 +6146,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2392.22</v>
+        <v>25155.65</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1480082-10-CM25</t>
+          <t>657-189-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,32 +6207,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>61.823.000-7</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>25155.65</v>
+        <v>3219.66</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>657-189-CM25</t>
+          <t>1057448-562-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6273,27 +6273,27 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.823.000-7</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3219.66</v>
+        <v>17822.87</v>
       </c>
     </row>
     <row r="97">
@@ -6553,7 +6553,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4728-618-CM25</t>
+          <t>1069417-2581-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,27 +6578,27 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.719.000-3</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
+          <t>Dirección  de Salud Municipal Chillán</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>52922.52</v>
+        <v>7943.25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1069417-2581-CM25</t>
+          <t>4728-618-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6639,27 +6639,27 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>60.719.000-3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>SUBSECRETARIA DE PESCA Y ACUICULTURA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7943.25</v>
+        <v>52922.52</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4605-220-CM25</t>
+          <t>1409-126-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6700,27 +6700,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.819.000-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>21485.18</v>
+        <v>28688.45</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>586-625-CM25</t>
+          <t>4605-220-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6761,27 +6761,27 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.819.000-5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>72850.23</v>
+        <v>21485.18</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2566-402-CM25</t>
+          <t>586-625-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6817,32 +6817,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.090.700-3</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHEPICA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>22060.22</v>
+        <v>72850.23</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1409-126-CM25</t>
+          <t>2566-402-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6878,22 +6878,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.090.700-3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE CHEPICA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>28688.45</v>
+        <v>22060.22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1051173-133-CM25</t>
+          <t>2859-1623-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6944,27 +6944,27 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>60.100.003-2</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>10082.57</v>
+        <v>19554.68</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1051173-134-CM25</t>
+          <t>2852-1175-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7005,17 +7005,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>60.100.003-2</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2248.86</v>
+        <v>6295.1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1306643-770-CM25</t>
+          <t>2854-1585-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3147.07</v>
+        <v>22580.25</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1026727-525-CM25</t>
+          <t>1186229-327-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7122,32 +7122,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>65.154.398-3</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>9115.280000000001</v>
+        <v>5530.82</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2733-726-CM25</t>
+          <t>4449-203-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>15447.39</v>
+        <v>6554.38</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1306643-774-CM25</t>
+          <t>1051173-133-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>60.100.003-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>21827.58</v>
+        <v>10082.57</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4449-203-CM25</t>
+          <t>2733-726-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>I MUNICIPALIDAD DE PENAFLOR</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6554.38</v>
+        <v>15447.39</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1186229-327-CM25</t>
+          <t>1026727-525-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7366,32 +7366,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>65.154.398-3</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE TARAPACA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5530.82</v>
+        <v>9115.280000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2854-1585-CM25</t>
+          <t>1306643-770-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7427,32 +7427,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>22580.25</v>
+        <v>3147.07</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2852-1175-CM25</t>
+          <t>1051173-134-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,17 +7493,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>60.100.003-2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>MINISTERIO SECRETARIA GENERAL DE LA PRESIDENCIA DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>6295.1</v>
+        <v>2248.86</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2859-1623-CM25</t>
+          <t>1306643-774-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7554,27 +7554,27 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>19554.68</v>
+        <v>21827.58</v>
       </c>
     </row>
     <row r="118">
@@ -7651,7 +7651,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1461054-456-CM25</t>
+          <t>1214069-258-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7676,27 +7676,27 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>70.878.100-2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>CORP MUNICIPAL DE CONCHALI DE EDUCACION SALUD Y ATENCION DE MENORES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>68864.67999999999</v>
+        <v>8230.040000000001</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1461054-457-CM25</t>
+          <t>2711-538-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7732,17 +7732,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>12307.81</v>
+        <v>10310.54</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>599-432-CM25</t>
+          <t>707428-153-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7793,17 +7793,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>15735.37</v>
+        <v>3616.89</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>654478-660-CM25</t>
+          <t>1306643-786-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6484.61</v>
+        <v>4240.59</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>707428-153-CM25</t>
+          <t>599-432-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7915,17 +7915,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3616.89</v>
+        <v>15735.37</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1214069-258-CM25</t>
+          <t>1461054-456-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,27 +7981,27 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.878.100-2</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CONCHALI DE EDUCACION SALUD Y ATENCION DE MENORES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>8230.040000000001</v>
+        <v>68864.67999999999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2711-538-CM25</t>
+          <t>654478-660-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8037,32 +8037,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>10310.54</v>
+        <v>6484.61</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1306643-786-CM25</t>
+          <t>1461054-457-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8103,27 +8103,27 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4240.59</v>
+        <v>12307.81</v>
       </c>
     </row>
     <row r="127">
@@ -8444,7 +8444,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2388-399-CM25</t>
+          <t>2388-398-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>5062.26</v>
+        <v>10124.52</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2388-398-CM25</t>
+          <t>2388-397-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>10124.52</v>
+        <v>13132.25</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2388-397-CM25</t>
+          <t>2388-399-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>13132.25</v>
+        <v>5062.26</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1347870-222-CM25</t>
+          <t>188-1098-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8647,32 +8647,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3189.02</v>
+        <v>58131.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1658-5413-CM25</t>
+          <t>2467-2083-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8713,27 +8713,27 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2544.7</v>
+        <v>9938.17</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>188-1098-CM25</t>
+          <t>2800-304-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,27 +8774,27 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>58131.5</v>
+        <v>17948.87</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2467-2083-CM25</t>
+          <t>1347870-222-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8830,32 +8830,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>9938.17</v>
+        <v>3189.02</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2800-304-CM25</t>
+          <t>1347870-221-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>17948.87</v>
+        <v>27671.21</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1214069-259-CM25</t>
+          <t>612-4410-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>70.878.100-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CONCHALI DE EDUCACION SALUD Y ATENCION DE MENORES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,28 +8972,32 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>58695.56</v>
+        <v>122114.87</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1347870-221-CM25</t>
+          <t>586-562-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9018,43 +9022,47 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>27671.21</v>
+        <v>173442.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>612-4410-CM25</t>
+          <t>1658-5413-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9074,52 +9082,48 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>122114.8726</v>
+        <v>2544.7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>586-562-CM25</t>
+          <t>1214069-259-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9144,47 +9148,43 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>70.878.100-2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CORP MUNICIPAL DE CONCHALI DE EDUCACION SALUD Y ATENCION DE MENORES</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>173442.5</v>
+        <v>58695.56</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>188-1129-CM25</t>
+          <t>1133353-36-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9204,32 +9204,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9239,13 +9239,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>7021</v>
+        <v>12921.62</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3958-277-CM25</t>
+          <t>986278-2017-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9265,32 +9265,32 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>34452.88</v>
+        <v>3318.49</v>
       </c>
     </row>
     <row r="146">
@@ -9367,7 +9367,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1133353-36-CM25</t>
+          <t>188-1129-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9422,13 +9422,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12921.62</v>
+        <v>7021</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>558869-293-CM25</t>
+          <t>986278-2016-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9448,32 +9448,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>60037.05</v>
+        <v>2677.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>986278-2017-CM25</t>
+          <t>3958-277-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9509,32 +9509,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>65.148.017-5</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9544,13 +9544,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3318.49</v>
+        <v>34452.88</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>986278-2016-CM25</t>
+          <t>3766-300-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>65.148.017-5</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9605,13 +9605,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2677.5</v>
+        <v>4283.94</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1195104-375-CM25</t>
+          <t>558869-293-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9631,32 +9631,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>62.000.920-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>21538.7</v>
+        <v>60037.05</v>
       </c>
     </row>
     <row r="152">
@@ -10038,7 +10038,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3766-300-CM25</t>
+          <t>1195104-375-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10058,32 +10058,32 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>62.000.920-2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10093,13 +10093,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>4283.94</v>
+        <v>21538.7</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1154491-11-CM25</t>
+          <t>1082957-696-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10119,17 +10119,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.216.000-7</t>
+          <t>62.000.680-7</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
+          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10154,13 +10154,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>18820.8</v>
+        <v>3890.59</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1082957-696-CM25</t>
+          <t>3251-1841-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10185,27 +10185,27 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>62.000.680-7</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3890.59</v>
+        <v>7752.97</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4649-261-CM25</t>
+          <t>1154491-11-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10241,32 +10241,32 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.216.000-7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10276,13 +10276,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5094.39</v>
+        <v>18820.8</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2328-1535-CM25</t>
+          <t>952751-21-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10302,32 +10302,32 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10337,13 +10337,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>24601.58</v>
+        <v>3600.8</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3251-1841-CM25</t>
+          <t>1305560-170-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10368,17 +10368,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10398,13 +10398,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7752.97</v>
+        <v>5065.24</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>952751-21-CM25</t>
+          <t>4649-261-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10424,32 +10424,32 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10459,13 +10459,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3600.8</v>
+        <v>5094.39</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2328-1536-CM25</t>
+          <t>2440-1947-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10485,32 +10485,32 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10520,13 +10520,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>6379.26</v>
+        <v>30154.18</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1306643-797-CM25</t>
+          <t>952751-20-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10546,32 +10546,32 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10581,13 +10581,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3392.69</v>
+        <v>21538.7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2440-1947-CM25</t>
+          <t>1305525-138-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10607,32 +10607,32 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.981.120-8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10642,13 +10642,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>30154.18</v>
+        <v>5520.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>952751-20-CM25</t>
+          <t>4053-830-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10668,32 +10668,32 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10703,13 +10703,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>21538.7</v>
+        <v>14443.03</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1305525-138-CM25</t>
+          <t>1393495-917-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.981.120-8</t>
+          <t>61.981.080-5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10764,13 +10764,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>5520.65</v>
+        <v>7529.13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1305560-170-CM25</t>
+          <t>1306643-797-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10795,17 +10795,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10825,13 +10825,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>5065.24</v>
+        <v>3392.69</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4053-830-CM25</t>
+          <t>2759-1181-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10846,37 +10846,37 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10886,13 +10886,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>14443.03</v>
+        <v>2441.88</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1393495-917-CM25</t>
+          <t>1431214-30-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10917,27 +10917,27 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.981.080-5</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>MUNICIPALIDAD DE QUILLÓN</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10947,13 +10947,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>7529.13</v>
+        <v>18240.78</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2759-1181-CM25</t>
+          <t>5416-1428-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10973,32 +10973,32 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11008,13 +11008,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2441.88</v>
+        <v>6007.6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1431214-30-CM25</t>
+          <t>1306643-802-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11039,17 +11039,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11069,13 +11069,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>18240.78</v>
+        <v>2441.88</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5416-1428-CM25</t>
+          <t>3888-684-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11095,32 +11095,32 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11130,13 +11130,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>6007.6</v>
+        <v>4584.64</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1306643-802-CM25</t>
+          <t>622844-87-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11176,12 +11176,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2441.88</v>
+        <v>44120.74</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3888-684-CM25</t>
+          <t>2934-124-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11217,32 +11217,32 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11252,13 +11252,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4584.64</v>
+        <v>6967.21</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>622844-87-CM25</t>
+          <t>2696-154-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11278,32 +11278,32 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11313,13 +11313,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>44120.74</v>
+        <v>36916.08</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3117-1633-CM25</t>
+          <t>2577-105-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11344,27 +11344,27 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>16659.76</v>
+        <v>3147.07</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2934-124-CM25</t>
+          <t>3117-1633-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11405,27 +11405,27 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11435,13 +11435,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>6967.21</v>
+        <v>16659.76</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2696-154-CM25</t>
+          <t>1375754-57-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11456,37 +11456,37 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.981.260-3</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11496,13 +11496,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>36916.08</v>
+        <v>4664.8</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2577-105-CM25</t>
+          <t>797305-115-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11542,12 +11542,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3147.07</v>
+        <v>2802.45</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>797305-115-CM25</t>
+          <t>797305-114-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11618,13 +11618,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2802.45</v>
+        <v>8833.99</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>797305-114-CM25</t>
+          <t>318-170-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11649,27 +11649,27 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>70.816.800-9</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11679,13 +11679,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>8833.99</v>
+        <v>2249.1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3604-2249-CM25</t>
+          <t>2832-3463-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11705,32 +11705,32 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.170.501-3</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11740,13 +11740,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>6254.64</v>
+        <v>12900.5</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>318-170-CM25</t>
+          <t>3604-2249-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11766,32 +11766,32 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>70.816.800-9</t>
+          <t>69.170.501-3</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LA REGION DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE MULCHEN DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11801,13 +11801,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2249.1</v>
+        <v>6254.64</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2832-3463-CM25</t>
+          <t>1013353-112-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11832,27 +11832,27 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>65.154.021-6</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11862,13 +11862,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>12900.5</v>
+        <v>57128.33</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1375754-57-CM25</t>
+          <t>2756-314-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11888,32 +11888,32 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.981.260-3</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11923,13 +11923,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4664.8</v>
+        <v>6271.3</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1013353-114-CM25</t>
+          <t>3933-138-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11949,32 +11949,32 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>65.154.021-6</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11984,13 +11984,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>16369.41</v>
+        <v>5035.89</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1057062-693-CM25</t>
+          <t>3933-139-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12010,32 +12010,32 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3273.33</v>
+        <v>9267.719999999999</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2756-314-CM25</t>
+          <t>1013353-114-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12071,32 +12071,32 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>65.154.021-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12106,13 +12106,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>6271.3</v>
+        <v>16369.41</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2756-313-CM25</t>
+          <t>4467-13-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12132,32 +12132,32 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12167,13 +12167,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>11297.8</v>
+        <v>72056.88</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4467-13-CM25</t>
+          <t>1057062-693-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12193,32 +12193,32 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12228,13 +12228,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>72056.88</v>
+        <v>3273.33</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3933-139-CM25</t>
+          <t>1233613-3793-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12249,37 +12249,37 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12289,13 +12289,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>9267.719999999999</v>
+        <v>28927.71</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3933-138-CM25</t>
+          <t>2788-2503-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12310,37 +12310,37 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12350,13 +12350,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>5035.89</v>
+        <v>3320.1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1013353-112-CM25</t>
+          <t>1233619-1413-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12381,27 +12381,27 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>65.154.021-6</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12411,13 +12411,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>57128.33</v>
+        <v>8231.879999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2428-1957-CM25</t>
+          <t>2440-2026-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12437,32 +12437,32 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12472,13 +12472,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>7363.13</v>
+        <v>17284.45</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1233613-3793-CM25</t>
+          <t>3560-505-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12498,32 +12498,32 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>28927.71</v>
+        <v>10178.78</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2788-2503-CM25</t>
+          <t>539119-10467-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12594,13 +12594,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3320.1</v>
+        <v>3658.29</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1233619-1413-CM25</t>
+          <t>2428-1957-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12625,27 +12625,27 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12655,13 +12655,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>8231.879999999999</v>
+        <v>7363.13</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2440-2026-CM25</t>
+          <t>593951-861-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12681,32 +12681,32 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12716,13 +12716,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>17284.45</v>
+        <v>11662</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3560-505-CM25</t>
+          <t>976-400-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12742,32 +12742,32 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12777,13 +12777,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>10178.78</v>
+        <v>3353.12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>539119-10467-CM25</t>
+          <t>2446-2136-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12808,43 +12808,47 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3658.29</v>
+        <v>128418.26</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>976-400-CM25</t>
+          <t>3606-207-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12864,32 +12868,32 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.967.400-6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MUNICIPALIDAD DE MULCHEN DIRECCION DE SALUD MUNICIPAL</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12899,13 +12903,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3353.12</v>
+        <v>12542.6</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2446-2136-CM25</t>
+          <t>4467-14-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12925,52 +12929,48 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>128418.255</v>
+        <v>24135.6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3553-578-CM25</t>
+          <t>5751-5704-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12995,17 +12995,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>22467.01</v>
+        <v>14644.5</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2279-1114-CM25</t>
+          <t>3992-296-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13051,32 +13051,32 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13086,13 +13086,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>5609.07</v>
+        <v>8396.639999999999</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3606-207-CM25</t>
+          <t>5062-7-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13117,27 +13117,27 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.967.400-6</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE MULCHEN DIRECCION DE SALUD MUNICIPAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13147,13 +13147,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>12542.6</v>
+        <v>40031.6</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4467-14-CM25</t>
+          <t>2703-1270-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13173,17 +13173,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13193,12 +13193,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13208,13 +13208,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>24135.6</v>
+        <v>6548.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5751-5704-CM25</t>
+          <t>3553-578-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13269,13 +13269,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>14644.5</v>
+        <v>22467.01</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3992-296-CM25</t>
+          <t>2279-1114-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13295,32 +13295,32 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13330,13 +13330,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>8396.639999999999</v>
+        <v>5609.07</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5062-7-CM25</t>
+          <t>1216062-1159-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13391,13 +13391,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>40031.6</v>
+        <v>9197.370000000001</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2703-1270-CM25</t>
+          <t>514848-1618-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13422,27 +13422,27 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13452,13 +13452,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>6548.33</v>
+        <v>3688.62</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>593951-861-CM25</t>
+          <t>1079969-204-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13483,12 +13483,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.944.800-6</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13498,12 +13498,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13513,13 +13513,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>11662</v>
+        <v>2793.53</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1216062-1159-CM25</t>
+          <t>1057858-22-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13539,17 +13539,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>61.608.600-6</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13574,13 +13574,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>9197.370000000001</v>
+        <v>56056.74</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>514848-1618-CM25</t>
+          <t>1348798-134-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13605,27 +13605,27 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCAC</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13635,13 +13635,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3688.62</v>
+        <v>63050.08</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1079969-204-CM25</t>
+          <t>1348798-135-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13666,12 +13666,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.944.800-6</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCAC</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13696,13 +13696,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2793.53</v>
+        <v>27193.53</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2380-2656-CM25</t>
+          <t>4455-1020-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13722,22 +13722,22 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13757,18 +13757,18 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>62134.11</v>
+        <v>9677.809999999999</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1348798-134-CM25</t>
+          <t>2380-2656-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2239-1-LR24</t>
+          <t>2239-5-LR25</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13783,32 +13783,32 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCAC</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13818,13 +13818,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>63050.08</v>
+        <v>62134.11</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1348798-135-CM25</t>
+          <t>1605-428-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCAC</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13879,13 +13879,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>27193.53</v>
+        <v>12747.28</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1057858-22-CM25</t>
+          <t>2366-4424-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13910,27 +13910,27 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.608.600-6</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13940,18 +13940,18 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>56056.74</v>
+        <v>10204.87</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4455-1020-CM25</t>
+          <t>4497-56-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13971,27 +13971,27 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.073.100-2</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>9677.809999999999</v>
+        <v>2509.56</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4202-41-CM25</t>
+          <t>2409-1891-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14027,32 +14027,32 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14062,13 +14062,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>7723.1</v>
+        <v>9661.129999999999</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2366-4424-CM25</t>
+          <t>4955-151-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14093,27 +14093,27 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Carabineros de Chile - Dirección General</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14123,13 +14123,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>10204.87</v>
+        <v>6181.03</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1417913-618-CM25</t>
+          <t>1020-465-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14149,17 +14149,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Cancelada por Comprador</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14169,12 +14169,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14184,13 +14184,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>6540.95</v>
+        <v>22716.24</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4497-56-CM25</t>
+          <t>539119-10250-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14215,12 +14215,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.073.100-2</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14245,13 +14245,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2509.56</v>
+        <v>5362.13</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2409-1891-CM25</t>
+          <t>3712-1029-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14306,13 +14306,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>9661.129999999999</v>
+        <v>4403</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4955-151-CM25</t>
+          <t>4202-41-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14367,13 +14367,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>6181.03</v>
+        <v>7723.1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1020-465-CM25</t>
+          <t>2759-1220-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14398,27 +14398,27 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14428,13 +14428,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>22716.24</v>
+        <v>2350.13</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>539119-10250-CM25</t>
+          <t>2688-403-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14449,37 +14449,37 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14489,13 +14489,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>5362.13</v>
+        <v>4719.25</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3712-1029-CM25</t>
+          <t>2385-1103-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -14520,27 +14520,27 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14550,13 +14550,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4403</v>
+        <v>10176.74</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1605-428-CM25</t>
+          <t>5586-4058-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14571,37 +14571,37 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14611,13 +14611,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>12747.28</v>
+        <v>17164.56</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5586-4058-CM25</t>
+          <t>5586-4059-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14672,13 +14672,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>17164.56</v>
+        <v>23526</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2759-1220-CM25</t>
+          <t>806208-121-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14703,27 +14703,27 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14733,13 +14733,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2350.13</v>
+        <v>9475.85</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2688-403-CM25</t>
+          <t>926-814-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14764,27 +14764,27 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.959.700-1</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>DIRECTORIO DE TRANSPORTE DE SANTIAGO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14794,13 +14794,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4719.25</v>
+        <v>11978.37</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2385-1103-CM25</t>
+          <t>1172239-108-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14825,27 +14825,27 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>62.000.820-6</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14855,13 +14855,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>10176.74</v>
+        <v>31594.5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5586-4059-CM25</t>
+          <t>1426039-50-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14881,32 +14881,32 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>23526</v>
+        <v>5105.1</v>
       </c>
     </row>
     <row r="238">
@@ -14983,7 +14983,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1426039-50-CM25</t>
+          <t>1233613-3836-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -15008,27 +15008,27 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15038,13 +15038,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5105.1</v>
+        <v>6518.23</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5952-441-CM25</t>
+          <t>1233613-3835-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15059,37 +15059,37 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15099,13 +15099,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>18022.5</v>
+        <v>26852.35</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>926-814-CM25</t>
+          <t>14-616-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15120,22 +15120,22 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.959.700-1</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIRECTORIO DE TRANSPORTE DE SANTIAGO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15145,12 +15145,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15160,13 +15160,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>11978.37</v>
+        <v>46410</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1172239-108-CM25</t>
+          <t>2440-2075-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15181,37 +15181,37 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>62.000.820-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15221,13 +15221,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>31594.5</v>
+        <v>7782.24</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1233613-3800-CM25</t>
+          <t>514848-1630-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15242,37 +15242,37 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15282,13 +15282,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>6997.2</v>
+        <v>3736.6</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1233613-3799-CM25</t>
+          <t>2440-2051-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15303,37 +15303,37 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15343,13 +15343,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>24490.2</v>
+        <v>9442.469999999999</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>806208-121-CM25</t>
+          <t>2471-2300-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15364,27 +15364,27 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15404,13 +15404,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>9475.85</v>
+        <v>12493.22</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1233613-3836-CM25</t>
+          <t>2471-2267-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15435,27 +15435,27 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15465,13 +15465,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>6518.23</v>
+        <v>23343.52</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1233613-3835-CM25</t>
+          <t>2471-2263-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15496,27 +15496,27 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15526,13 +15526,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>26852.35</v>
+        <v>12356.96</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>14-616-CM25</t>
+          <t>1339159-133-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.981.070-8</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Servicio Local de Educación Pública Santa Rosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15572,12 +15572,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15587,13 +15587,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>46410</v>
+        <v>21278.02</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2440-2075-CM25</t>
+          <t>1233623-1319-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15613,32 +15613,32 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15648,13 +15648,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>7782.24</v>
+        <v>6294.15</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2780-539-CM25</t>
+          <t>5598-60-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15674,32 +15674,32 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -15709,555 +15709,6 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2454.27</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>514848-1630-CM25</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>69.190.100-9</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M251" s="2" t="n">
-        <v>3736.6</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2471-2300-CM25</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>69.140.900-7</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M252" s="2" t="n">
-        <v>12493.22</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2440-2051-CM25</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>69.100.100-8</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>Tic Services SPA</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M253" s="2" t="n">
-        <v>9442.469999999999</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2471-2267-CM25</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>69.140.900-7</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>Sumatec Ltda.</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M254" s="2" t="n">
-        <v>23343.52</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2471-2263-CM25</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>69.140.900-7</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M255" s="2" t="n">
-        <v>12356.96</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>2484-772-CM25</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>No aceptada</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>69.071.301-2</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M256" s="2" t="n">
-        <v>12961.27</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>1339159-133-CM25</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>61.981.070-8</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M257" s="2" t="n">
-        <v>21278.02</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>1233623-1319-CM25</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>61.980.920-3</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>I.I.A. Ltda.</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M258" s="2" t="n">
-        <v>6294.15</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>5598-60-CM25</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>60.910.000-1</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE CHILE</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M259" s="2" t="n">
         <v>46945.5</v>
       </c>
     </row>
